--- a/planning/반입_체크리스트.xlsx
+++ b/planning/반입_체크리스트.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -108,6 +108,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -475,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -860,7 +866,7 @@
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>설탕량 미정</t>
+          <t>설탕량 미정. 냉장고를 안 가져가서 라떼 통·우유 차갑게 보관할 방법 필요(아이스박스 등). 오트뮤·저지우유 현장 무상 지원 신청함</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr"/>
@@ -940,22 +946,22 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>1식</t>
+          <t>머신·온수기·그라인더 4</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>미주문</t>
+          <t>일부 확정</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>에스프레소 머신·그라인더·테이블 냉장고·온수기·피처린서</t>
+          <t>MRC 1그룹 가변압 에스프레소 머신·진성 JS-1 온수기(확정), 그라인더 4대(미정)</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>모델·소비전력 미확인 → 5kW 안인지 계산 필요</t>
+          <t>그라인더 대여처 빨리 확정. 냉장고는 안 가져감. 전기 최종 2kW(대표 판단: 머신·온수기는 예열 뒤 약 100W, 그라인더 동시 사용 안 함)</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr"/>
@@ -1073,17 +1079,17 @@
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>확인 필요</t>
+          <t>신청 완료</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>드립백 현장 결제(원두는 아임웹 QR)</t>
+          <t>네이버페이 커넥트 무상 대여 + 행사용 카드단말기 지원</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>준비 방법 미정</t>
+          <t>와이파이 도시락·행사 후 반납/무상 여부 업체 회신 대기</t>
         </is>
       </c>
       <c r="G22" s="8" t="inlineStr"/>
@@ -1271,149 +1277,149 @@
       <c r="G28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>물품·기물</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>DK4 정수필터 설치 부자재</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>1식</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>준비 필요</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>파라곤필터 DK4(11/10 C224 수령) 머신·온수기 연결</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>튜빙·피팅·호스·테프론 테이프 — 머신·온수기 입수구 규격 확인</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>물품·기물</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>아이스박스 + 아이스팩</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>2개 이상</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>준비 필요</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>냉장고 없이 구수 라떼 통·우유 차갑게 보관</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>아이스팩 교체·보충 방법 정하기</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>물품·기물</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>B2B 상담 키트</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>1파우치</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>준비 필요</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>바이어 라운지(C501 앞) 상담용</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>명함·소개서·원두 샘플·내부용 납품가표·펜·상담 기록지</t>
+        </is>
+      </c>
+      <c r="G31" s="10" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>2) 인쇄물</t>
         </is>
       </c>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="5" t="n"/>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="5" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>인쇄물</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>소반 스탠딩 안내판</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>4종 + 여분</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>디자인 중</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>소반마다 커피 개요(이름·한상 이름·향미·리필/드립백 안내)</t>
         </is>
       </c>
-      <c r="F30" s="6" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <t>액자틀 4·높이 조절판 4·거치대 4 구매 완료</t>
         </is>
       </c>
-      <c r="G30" s="6" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>인쇄물</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>소반 카드(맛 보는 법)</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>4종</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>디자인 중</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t>밥그릇 옆 90×90mm — 3단계 맛보는 법 + 회원가입 덤 안내</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t>허벌·구수·보통 향미 문구를 커핑 노트로 바꾸기</t>
-        </is>
-      </c>
-      <c r="G31" s="8" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>인쇄물</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>원두 김장 계산 카드</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>2~3장</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>확인 필요</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>판매대 — "하루 1잔이면 한 달 약 450g"</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t>비용 탭 목록에서 빠짐</t>
-        </is>
-      </c>
-      <c r="G32" s="8" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>인쇄물</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>원두 주문 QR 카드</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>2장</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>확인 필요</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t>판매대 — 아임웹 현장 주문(무료배송·드립백 2개 덤)</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t>비용 탭 목록에서 빠짐. 덤 문구 넣기</t>
-        </is>
-      </c>
-      <c r="G33" s="8" t="inlineStr"/>
+      <c r="G33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
@@ -1423,27 +1429,27 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>B2B 상담 QR 카드</t>
+          <t>소반 카드(맛 보는 법)</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>2장</t>
+          <t>4종</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>확인 필요</t>
+          <t>디자인 중</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>비즈니스데이(수·목) 납품 상담</t>
+          <t>밥그릇 옆 90×90mm — 3단계 맛보는 법 + 회원가입 덤 안내</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>비용 탭 목록에서 빠짐</t>
+          <t>허벌·구수·보통 향미 문구를 커핑 노트로 바꾸기</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr"/>
@@ -1456,12 +1462,12 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>B2B 안내 브로셔</t>
+          <t>원두 김장 계산 카드</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>수량 미정</t>
+          <t>2~3장</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -1471,7 +1477,7 @@
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>사장님께 드림 → 다음 주 전화 연락</t>
+          <t>판매대 — "하루 1잔이면 한 달 약 450g"</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
@@ -1489,12 +1495,12 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>메뉴판(백반 0원)</t>
+          <t>원두 주문 QR 카드</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>1장</t>
+          <t>2장</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -1504,12 +1510,12 @@
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>시음 무료 안내</t>
+          <t>판매대 — 아임웹 현장 주문(무료배송·드립백 2개 덤)</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>비용 탭 목록에서 빠짐</t>
+          <t>비용 탭 목록에서 빠짐. 덤 문구 넣기</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr"/>
@@ -1522,12 +1528,12 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>쿠폰 카드</t>
+          <t>B2B 상담 QR 카드</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2장</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
@@ -1537,43 +1543,63 @@
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>(수저 봉투 속 쿠폰이었음)</t>
+          <t>비즈니스데이(수·목) 납품 상담</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>수저 봉투를 안 하면 필요 없음</t>
+          <t>비용 탭 목록에서 빠짐</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>3) 부착물</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="n"/>
-      <c r="C38" s="5" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="5" t="n"/>
-      <c r="F38" s="5" t="n"/>
-      <c r="G38" s="5" t="n"/>
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>인쇄물</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>B2B 안내 브로셔</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>수량 미정</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>사장님께 드림 → 다음 주 전화 연락</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>비용 탭 목록에서 빠짐</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>부착물</t>
+          <t>인쇄물</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>상부 간판·벽면 그래픽</t>
+          <t>메뉴판(백반 0원)</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>1식</t>
+          <t>1장</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
@@ -1583,12 +1609,12 @@
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>부스 정면 인지(메쎄바우 출력)</t>
+          <t>시음 무료 안내</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>비용 탭에서 빠짐. 부스 추가옵션 마감(10/28) 지남 — 신청 여부 확인</t>
+          <t>비용 탭 목록에서 빠짐</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr"/>
@@ -1596,234 +1622,222 @@
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
+          <t>인쇄물</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>쿠폰 카드</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>(수저 봉투 속 쿠폰이었음)</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>수저 봉투를 안 하면 필요 없음</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>3) 부착물</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n"/>
+      <c r="C41" s="5" t="n"/>
+      <c r="D41" s="5" t="n"/>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="n"/>
+      <c r="G41" s="5" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
           <t>부착물</t>
         </is>
       </c>
-      <c r="B40" s="9" t="inlineStr">
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>상부 간판·벽면 그래픽</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>1식</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>부스 정면 인지(메쎄바우 출력)</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>비용 탭에서 빠짐. 부스 추가옵션 마감(10/28) 지남 — 신청 여부 확인</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>부착물</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
         <is>
           <t>뒷벽 원산지 표시판</t>
         </is>
       </c>
-      <c r="C40" s="8" t="inlineStr">
+      <c r="C43" s="8" t="inlineStr">
         <is>
           <t>1장</t>
         </is>
       </c>
-      <c r="D40" s="8" t="inlineStr">
+      <c r="D43" s="8" t="inlineStr">
         <is>
           <t>확인 필요</t>
         </is>
       </c>
-      <c r="E40" s="8" t="inlineStr">
+      <c r="E43" s="8" t="inlineStr">
         <is>
           <t>식당 원산지 표시처럼 4종 원산지 + 볶은 곳 여수</t>
         </is>
       </c>
-      <c r="F40" s="8" t="inlineStr">
+      <c r="F43" s="8" t="inlineStr">
         <is>
           <t>비용 탭에서 빠짐. 배합은 자사몰 기준, 허벌 67:33</t>
         </is>
       </c>
-      <c r="G40" s="8" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>부착물</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>대기줄 안내판(A4)</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>2장</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>확인 필요</t>
-        </is>
-      </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>줄 서는 동안 회원가입 QR + 인스타 @gachi_coffee</t>
-        </is>
-      </c>
-      <c r="F41" s="6" t="inlineStr">
-        <is>
-          <t>원고: planning/대기줄_안내판_기안.md</t>
-        </is>
-      </c>
-      <c r="G41" s="6" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>부착물</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>숫자판 "오늘 대접한 손님"</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>1개</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>미주문</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>실시간 숫자, 사진 찍기 좋은 장면</t>
-        </is>
-      </c>
-      <c r="F42" s="6" t="inlineStr">
-        <is>
-          <t>집게 보드 19,500원 미주문</t>
-        </is>
-      </c>
-      <c r="G42" s="6" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>4) 가구</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="n"/>
-      <c r="C43" s="5" t="n"/>
-      <c r="D43" s="5" t="n"/>
-      <c r="E43" s="5" t="n"/>
-      <c r="F43" s="5" t="n"/>
-      <c r="G43" s="5" t="n"/>
+      <c r="G43" s="8" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>가구</t>
+          <t>부착물</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>시음 책상</t>
+          <t>대기줄 안내판(A4)</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>1개</t>
+          <t>2장</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>구매 완료</t>
+          <t>확인 필요</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>소반 4상을 올리는 상</t>
-        </is>
-      </c>
-      <c r="F44" s="6" t="inlineStr"/>
+          <t>줄 서는 동안 회원가입 QR + 인스타 @gachi_coffee</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>원고: planning/대기줄_안내판_기안.md</t>
+        </is>
+      </c>
       <c r="G44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
+          <t>부착물</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>숫자판 "오늘 대접한 손님"</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>미주문</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>실시간 숫자, 사진 찍기 좋은 장면</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>집게 보드 19,500원 미주문</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>4) 가구</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n"/>
+      <c r="C46" s="5" t="n"/>
+      <c r="D46" s="5" t="n"/>
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="5" t="n"/>
+      <c r="G46" s="5" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
           <t>가구</t>
         </is>
       </c>
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>시음 의자</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>3개</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>시음 책상</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>구매 완료</t>
         </is>
       </c>
-      <c r="E45" s="6" t="inlineStr">
-        <is>
-          <t>한 회차 3명</t>
-        </is>
-      </c>
-      <c r="F45" s="6" t="inlineStr"/>
-      <c r="G45" s="6" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>가구</t>
-        </is>
-      </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>제조 책상</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>1개</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>구매 완료</t>
-        </is>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>추출·라떼 준비</t>
-        </is>
-      </c>
-      <c r="F46" s="6" t="inlineStr"/>
-      <c r="G46" s="6" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="8" t="inlineStr">
-        <is>
-          <t>가구</t>
-        </is>
-      </c>
-      <c r="B47" s="9" t="inlineStr">
-        <is>
-          <t>판매대 책상</t>
-        </is>
-      </c>
-      <c r="C47" s="8" t="inlineStr">
-        <is>
-          <t>2개</t>
-        </is>
-      </c>
-      <c r="D47" s="8" t="inlineStr">
-        <is>
-          <t>구매 완료</t>
-        </is>
-      </c>
-      <c r="E47" s="8" t="inlineStr">
-        <is>
-          <t>드립백·원두 주문 안내</t>
-        </is>
-      </c>
-      <c r="F47" s="8" t="inlineStr">
-        <is>
-          <t>3×2m 부스에 시음·제조·판매대 2·인포데스크(주최측)까지 들어가는지 배치도로 확인</t>
-        </is>
-      </c>
-      <c r="G47" s="8" t="inlineStr"/>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>소반 4상을 올리는 상</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr"/>
+      <c r="G47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -1833,12 +1847,12 @@
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>책상 가릴 천</t>
+          <t>시음 의자</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>1개</t>
+          <t>3개</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
@@ -1848,7 +1862,7 @@
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>책상 다리·짐 가리기</t>
+          <t>한 회차 3명</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr"/>
@@ -1862,7 +1876,7 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>포인트천</t>
+          <t>제조 책상</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -1877,44 +1891,135 @@
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>상차림 바탕(사진 속 노란 천)</t>
+          <t>추출·라떼 준비</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr"/>
       <c r="G49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="6" t="inlineStr">
+      <c r="A50" s="8" t="inlineStr">
         <is>
           <t>가구</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>판매대 책상</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>2개</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>구매 완료</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>드립백·원두 주문 안내</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>3×2m 부스에 시음·제조·판매대 2·인포데스크(주최측)까지 들어가는지 배치도로 확인</t>
+        </is>
+      </c>
+      <c r="G50" s="8" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>가구</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>책상 가릴 천</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>구매 완료</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>책상 다리·짐 가리기</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr"/>
+      <c r="G51" s="6" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>가구</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>포인트천</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>1개</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>구매 완료</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>상차림 바탕(사진 속 노란 천)</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr"/>
+      <c r="G52" s="6" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>가구</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>주최측 제공: 인포데스크·접의자 1조</t>
         </is>
       </c>
-      <c r="C50" s="6" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D50" s="6" t="inlineStr">
+      <c r="D53" s="6" t="inlineStr">
         <is>
           <t>가져갈 필요 없음</t>
         </is>
       </c>
-      <c r="E50" s="6" t="inlineStr">
+      <c r="E53" s="6" t="inlineStr">
         <is>
           <t>부스 기본 제공</t>
         </is>
       </c>
-      <c r="F50" s="6" t="inlineStr">
+      <c r="F53" s="6" t="inlineStr">
         <is>
           <t>목공벽·암스팟 2도 제공</t>
         </is>
       </c>
-      <c r="G50" s="6" t="inlineStr"/>
+      <c r="G53" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/planning/반입_체크리스트.xlsx
+++ b/planning/반입_체크리스트.xlsx
@@ -656,17 +656,17 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>작은 은 주전자</t>
+          <t>하리오 서버 (주전자 대신)</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>6개(4+여분2)</t>
+          <t>상마다 1 + 여분 (수량 확인)</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>미주문</t>
+          <t>가져감</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>미주문</t>
+          <t>10/28: 은 주전자 안 삼 → 하리오 서버</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr"/>
@@ -767,7 +767,7 @@
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>비용 탭 "원두 원물(12개, 100,000원)"과 같은 것인지 확인</t>
+          <t>비용 탭 "원두 원물(12개, 100,000원)"과 같은 것인지 확인 / 담당 효진·찬양</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr"/>
@@ -1211,7 +1211,11 @@
           <t>행주·세제·수세미·장갑·키친타월·물티슈</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr"/>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>담당 서준·다빈</t>
+        </is>
+      </c>
       <c r="G26" s="6" t="inlineStr"/>
     </row>
     <row r="27">

--- a/planning/반입_체크리스트.xlsx
+++ b/planning/반입_체크리스트.xlsx
@@ -507,6 +507,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -694,7 +695,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>5,000개</t>
+          <t>6,000개(5,000 + 1,000 추가)</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -1448,7 +1449,7 @@
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>밥그릇 옆 90×90mm — 3단계 맛보는 법 + 회원가입 덤 안내</t>
+          <t>밥그릇 옆 90×90mm — 3단계 맛보는 법 + 아래 "남도에선 손님을 빈손으로 보내지 않아요"·팔로우 덤(10/29 확정)</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
@@ -1514,7 +1515,7 @@
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>판매대 — 아임웹 현장 주문(무료배송·드립백 2개 덤)</t>
+          <t>판매대 — 아임웹 현장 주문(무료배송·드립백 증정)</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
@@ -1758,7 +1759,7 @@
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>줄 서는 동안 회원가입 QR + 인스타 @gachi_coffee</t>
+          <t>줄 서는 동안 인스타 @gachi_coffee 팔로우 QR → 나가실 때 노트(10/28)</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
